--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e_w331275940-765_IND</t>
+          <t>e_Vadodara_IND</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e_w420797421-765_IND</t>
+          <t>e_Sikandarabad_IND</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_w386153973-765_IND</t>
+          <t>e_Dharmapuri_IND</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -624,7 +624,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e_w759521252-765_IND</t>
+          <t>e_Medinipur_IND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e_w315823978-765_IND</t>
+          <t>e_Kurnool_IND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e_w293597835-765_IND</t>
+          <t>e_Solapur_IND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e_w311118424-765_IND</t>
+          <t>e_Fatehpur_IND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>e_IN684-765_IND</t>
+          <t>e_Rajahmundry_IND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +718,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e_w209826798-765_IND</t>
+          <t>e_Indore_IND</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e_w372701897-765_IND</t>
+          <t>e_Moga_IND</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -807,7 +807,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e_w353914865-765_IND</t>
+          <t>e_Korba_IND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>e_w203673991-400_IND</t>
+          <t>e_Tezpur_IND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>e_w201845280-765_IND</t>
+          <t>e_Wardha_IND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -933,7 +933,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e_w688672711-765_IND</t>
+          <t>e_Bhuj_IND</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
